--- a/data/Characters.xlsx
+++ b/data/Characters.xlsx
@@ -478,13 +478,13 @@
         <v>char_001</v>
       </c>
       <c r="C2" t="str">
-        <v>星星使者</v>
+        <v>玉蝉仙</v>
       </c>
       <c r="D2" t="str">
         <v>N</v>
       </c>
       <c r="E2" t="str">
-        <v>初学者的第一个伙伴</v>
+        <v>华夏·玉器灵，自带护盾再生，新手的第一位伙伴</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -549,13 +549,13 @@
         <v>char_002</v>
       </c>
       <c r="C3" t="str">
-        <v>星光战士</v>
+        <v>鼎魂</v>
       </c>
       <c r="D3" t="str">
         <v>R</v>
       </c>
       <c r="E3" t="str">
-        <v>勇敢的战士，擅长连击</v>
+        <v>华夏·青铜灵，高攻高防，擅长正面战斗</v>
       </c>
       <c r="F3">
         <v>150</v>
@@ -620,13 +620,13 @@
         <v>char_003</v>
       </c>
       <c r="C4" t="str">
-        <v>星界法师</v>
+        <v>青花仙</v>
       </c>
       <c r="D4" t="str">
         <v>SR</v>
       </c>
       <c r="E4" t="str">
-        <v>精通星辰魔法的法师</v>
+        <v>华夏·瓷器灵，脆皮高暴击，灵气回复快</v>
       </c>
       <c r="F4">
         <v>80</v>
@@ -691,13 +691,13 @@
         <v>char_004</v>
       </c>
       <c r="C5" t="str">
-        <v>流星射手</v>
+        <v>剑魄</v>
       </c>
       <c r="D5" t="str">
         <v>R</v>
       </c>
       <c r="E5" t="str">
-        <v>精准的远程射手</v>
+        <v>华夏·青铜灵，重击流，蓄力速度+30%</v>
       </c>
       <c r="F5">
         <v>100</v>
@@ -762,13 +762,13 @@
         <v>char_005</v>
       </c>
       <c r="C6" t="str">
-        <v>龙骑士</v>
+        <v>水墨仙</v>
       </c>
       <c r="D6" t="str">
         <v>SSR</v>
       </c>
       <c r="E6" t="str">
-        <v>驾驭龙之力的骑士</v>
+        <v>华夏·书画灵，控制型，减速邪灵</v>
       </c>
       <c r="F6">
         <v>200</v>
@@ -833,13 +833,13 @@
         <v>char_006</v>
       </c>
       <c r="C7" t="str">
-        <v>星之女神</v>
+        <v>金乌</v>
       </c>
       <c r="D7" t="str">
         <v>UR</v>
       </c>
       <c r="E7" t="str">
-        <v>星辰的化身，最强的存在</v>
+        <v>华夏·金银灵，灵币加成，掉落翻倍</v>
       </c>
       <c r="F7">
         <v>300</v>
@@ -904,13 +904,13 @@
         <v>char_007</v>
       </c>
       <c r="C8" t="str">
-        <v>暗影刺客</v>
+        <v>冰裂使</v>
       </c>
       <c r="D8" t="str">
         <v>SR</v>
       </c>
       <c r="E8" t="str">
-        <v>暗夜中的致命杀手</v>
+        <v>华夏·瓷器灵，高暴击，冰属性攻击</v>
       </c>
       <c r="F8">
         <v>90</v>
@@ -975,13 +975,13 @@
         <v>char_008</v>
       </c>
       <c r="C9" t="str">
-        <v>星盾守护者</v>
+        <v>璧灵</v>
       </c>
       <c r="D9" t="str">
         <v>R</v>
       </c>
       <c r="E9" t="str">
-        <v>坚不可摧的防御专家</v>
+        <v>华夏·玉器灵，均衡型，自带护盾</v>
       </c>
       <c r="F9">
         <v>250</v>
@@ -1046,13 +1046,13 @@
         <v>char_009</v>
       </c>
       <c r="C10" t="str">
-        <v>星灵召唤师</v>
+        <v>云锦仙</v>
       </c>
       <c r="D10" t="str">
         <v>SSR</v>
       </c>
       <c r="E10" t="str">
-        <v>召唤星辰之力作战</v>
+        <v>华夏·织绣灵，辅助型，团队增益</v>
       </c>
       <c r="F10">
         <v>110</v>
@@ -1117,13 +1117,13 @@
         <v>char_010</v>
       </c>
       <c r="C11" t="str">
-        <v>狂星战神</v>
+        <v>狂草客</v>
       </c>
       <c r="D11" t="str">
         <v>SSR</v>
       </c>
       <c r="E11" t="str">
-        <v>越战越勇的狂战士</v>
+        <v>华夏·书画灵，控制型，封印邪灵</v>
       </c>
       <c r="F11">
         <v>180</v>
@@ -1188,13 +1188,13 @@
         <v>char_011</v>
       </c>
       <c r="C12" t="str">
-        <v>圣星贤者</v>
+        <v>鎏光使</v>
       </c>
       <c r="D12" t="str">
         <v>UR</v>
       </c>
       <c r="E12" t="str">
-        <v>掌握星辰奥秘的贤者</v>
+        <v>华夏·金银灵，灵币加成，暴击掉落</v>
       </c>
       <c r="F12">
         <v>150</v>
@@ -1259,13 +1259,13 @@
         <v>char_012</v>
       </c>
       <c r="C13" t="str">
-        <v>流星忍者</v>
+        <v>仕女魂</v>
       </c>
       <c r="D13" t="str">
         <v>SR</v>
       </c>
       <c r="E13" t="str">
-        <v>极速的星辰忍者</v>
+        <v>华夏·书画灵，辅助型，团队灵力回复</v>
       </c>
       <c r="F13">
         <v>85</v>
@@ -1330,13 +1330,13 @@
         <v>char_013</v>
       </c>
       <c r="C14" t="str">
-        <v>星辰祭司</v>
+        <v>琮灵</v>
       </c>
       <c r="D14" t="str">
         <v>R</v>
       </c>
       <c r="E14" t="str">
-        <v>虔诚的星辰信仰者</v>
+        <v>华夏·玉器灵，均衡型，灵力回复快</v>
       </c>
       <c r="F14">
         <v>120</v>
@@ -1401,13 +1401,13 @@
         <v>char_014</v>
       </c>
       <c r="C15" t="str">
-        <v>圣星骑士</v>
+        <v>镜灵</v>
       </c>
       <c r="D15" t="str">
         <v>SR</v>
       </c>
       <c r="E15" t="str">
-        <v>信仰与力量并存的骑士</v>
+        <v>华夏·青铜灵，重击流，满蓄额外触发灵光</v>
       </c>
       <c r="F15">
         <v>200</v>
@@ -1472,13 +1472,13 @@
         <v>char_015</v>
       </c>
       <c r="C16" t="str">
-        <v>星域猎人</v>
+        <v>银蟾</v>
       </c>
       <c r="D16" t="str">
         <v>R</v>
       </c>
       <c r="E16" t="str">
-        <v>追踪星辰的猎手</v>
+        <v>华夏·金银灵，灵币加成，净化额外掉落</v>
       </c>
       <c r="F16">
         <v>95</v>
@@ -1543,13 +1543,13 @@
         <v>char_016</v>
       </c>
       <c r="C17" t="str">
-        <v>星辰魔女</v>
+        <v>釉里红</v>
       </c>
       <c r="D17" t="str">
         <v>SSR</v>
       </c>
       <c r="E17" t="str">
-        <v>操控星辰魔法的魔女</v>
+        <v>华夏·瓷器灵，高暴击，火属性攻击</v>
       </c>
       <c r="F17">
         <v>75</v>
@@ -1614,13 +1614,13 @@
         <v>char_017</v>
       </c>
       <c r="C18" t="str">
-        <v>星拳武僧</v>
+        <v>缂丝娘</v>
       </c>
       <c r="D18" t="str">
         <v>SR</v>
       </c>
       <c r="E18" t="str">
-        <v>以拳悟道的武僧</v>
+        <v>华夏·织绣灵，辅助型，全队防御提升</v>
       </c>
       <c r="F18">
         <v>140</v>
@@ -1685,13 +1685,13 @@
         <v>char_018</v>
       </c>
       <c r="C19" t="str">
-        <v>星辰元素师</v>
+        <v>苏绣魂</v>
       </c>
       <c r="D19" t="str">
         <v>SSR</v>
       </c>
       <c r="E19" t="str">
-        <v>掌控元素之力的法师</v>
+        <v>华夏·织绣灵，辅助型，全队攻击提升</v>
       </c>
       <c r="F19">
         <v>90</v>
@@ -1756,13 +1756,13 @@
         <v>char_019</v>
       </c>
       <c r="C20" t="str">
-        <v>星陨死灵师</v>
+        <v>掷铁饼者</v>
       </c>
       <c r="D20" t="str">
         <v>SSR</v>
       </c>
       <c r="E20" t="str">
-        <v>操控亡灵之力的术士</v>
+        <v>希腊·追求完美人体，暴击时驱逐邪灵增益</v>
       </c>
       <c r="F20">
         <v>100</v>
@@ -1827,13 +1827,13 @@
         <v>char_020</v>
       </c>
       <c r="C21" t="str">
-        <v>星时光使</v>
+        <v>罗塞塔石碑灵</v>
       </c>
       <c r="D21" t="str">
         <v>UR</v>
       </c>
       <c r="E21" t="str">
-        <v>操控时间的神秘存在</v>
+        <v>埃及·破译文明密码，可复制邪灵技能</v>
       </c>
       <c r="F21">
         <v>130</v>
@@ -1898,13 +1898,13 @@
         <v>char_021</v>
       </c>
       <c r="C22" t="str">
-        <v>星途流浪者</v>
+        <v>圣甲虫使</v>
       </c>
       <c r="D22" t="str">
         <v>N</v>
       </c>
       <c r="E22" t="str">
-        <v>流浪星际的神秘旅人</v>
+        <v>埃及·圣甲虫化身，沙金之力</v>
       </c>
       <c r="F22">
         <v>110</v>
@@ -1969,13 +1969,13 @@
         <v>char_022</v>
       </c>
       <c r="C23" t="str">
-        <v>星炼金术师</v>
+        <v>法老金棺</v>
       </c>
       <c r="D23" t="str">
         <v>SR</v>
       </c>
       <c r="E23" t="str">
-        <v>炼制星辰之力的学者</v>
+        <v>埃及·诅咒叠层，凋零倒计时</v>
       </c>
       <c r="F23">
         <v>105</v>
@@ -2040,13 +2040,13 @@
         <v>char_023</v>
       </c>
       <c r="C24" t="str">
-        <v>星血伯爵</v>
+        <v>世界蛇·耶梦加得</v>
       </c>
       <c r="D24" t="str">
         <v>SSR</v>
       </c>
       <c r="E24" t="str">
-        <v>汲取星辰之力的吸血鬼</v>
+        <v>北欧·毒雾扩散，缠绕邪灵</v>
       </c>
       <c r="F24">
         <v>160</v>
@@ -2111,13 +2111,13 @@
         <v>char_024</v>
       </c>
       <c r="C25" t="str">
-        <v>天穹星神</v>
+        <v>羽蛇神</v>
       </c>
       <c r="D25" t="str">
         <v>UR</v>
       </c>
       <c r="E25" t="str">
-        <v>来自天穹的至高存在</v>
+        <v>玛雅·时间回溯，星辰陨落</v>
       </c>
       <c r="F25">
         <v>280</v>
@@ -2182,13 +2182,13 @@
         <v>char_025</v>
       </c>
       <c r="C26" t="str">
-        <v>虚空帝皇</v>
+        <v>青铜鼎灵</v>
       </c>
       <c r="D26" t="str">
         <v>LR</v>
       </c>
       <c r="E26" t="str">
-        <v>虚空之主，掌控时空与混沌之力</v>
+        <v>华夏·守护灵，分裂、封印、灵压场</v>
       </c>
       <c r="F26">
         <v>400</v>
@@ -2253,13 +2253,13 @@
         <v>char_026</v>
       </c>
       <c r="C27" t="str">
-        <v>星际旅人</v>
+        <v>雅典娜神像</v>
       </c>
       <c r="D27" t="str">
         <v>SP</v>
       </c>
       <c r="E27" t="str">
-        <v>穿越星海的旅行者，每场随机获得宇宙祝福</v>
+        <v>希腊·奥林匹斯守护神，雷电裁决</v>
       </c>
       <c r="F27">
         <v>260</v>
